--- a/models/templates/2026-05-10-coca-cola-financials.xlsx
+++ b/models/templates/2026-05-10-coca-cola-financials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/47cbdb28c43eca10/Tài liệu/GitHub/Corporate-Finance/models/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CB1A3533-58D9-4CDF-A9BF-92729DA9008F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D5351CE-6C92-4B83-B370-D4653001E278}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CB1A3533-58D9-4CDF-A9BF-92729DA9008F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD2FE666-523D-4237-A210-DB9A6E5C2007}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="322">
   <si>
     <t>Ratios &amp; Derived Inputs</t>
   </si>
@@ -1021,9 +1021,6 @@
   </si>
   <si>
     <t>Share Price</t>
-  </si>
-  <si>
-    <t>[FY-end closing price]</t>
   </si>
   <si>
     <t>Shares Outstanding</t>
@@ -3480,7 +3477,7 @@
         <v>287</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3488,7 +3485,7 @@
         <v>288</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3496,7 +3493,7 @@
         <v>289</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3504,7 +3501,7 @@
         <v>290</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3512,7 +3509,7 @@
         <v>291</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" x14ac:dyDescent="0.45">
@@ -3520,7 +3517,7 @@
         <v>292</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3528,7 +3525,7 @@
         <v>293</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="15" x14ac:dyDescent="0.45">
@@ -3551,77 +3548,77 @@
       <c r="B13" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>298</v>
+      <c r="C13" s="4">
+        <v>69.91</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="15" x14ac:dyDescent="0.45">
       <c r="B14" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="15" x14ac:dyDescent="0.45">
       <c r="B16" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15" x14ac:dyDescent="0.45">
       <c r="B22" s="43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
   </sheetData>
